--- a/Data/Order_data.xlsx
+++ b/Data/Order_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\datn\Data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{63123126-8F36-4C99-93C6-66C6B078E62F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210CCBC6-BE11-4DEA-BC02-6FCCD3DD1029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4206AC39-6B44-4762-8F45-A4B4FD4DED31}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="27">
   <si>
     <t>Họ và tên</t>
   </si>
@@ -67,27 +67,12 @@
     <t>Đặt hàng thành công</t>
   </si>
   <si>
-    <t>Vui lòng nhập email</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập số điện thoại</t>
-  </si>
-  <si>
-    <t>Vui lòng nhập địa chỉ</t>
-  </si>
-  <si>
     <t>mai34</t>
   </si>
   <si>
-    <t>Email không hợp lệ</t>
-  </si>
-  <si>
     <t>mai@gmai</t>
   </si>
   <si>
-    <t>Số điện thoại không hợp lệ</t>
-  </si>
-  <si>
     <t>0987asf786</t>
   </si>
   <si>
@@ -97,13 +82,25 @@
     <t xml:space="preserve">Mai </t>
   </si>
   <si>
-    <t>Vui lòng nhập họ tên đầy đủ</t>
-  </si>
-  <si>
     <t>$$$%%%</t>
   </si>
   <si>
-    <t>Địa chỉ không hợp lệ</t>
+    <t>Vui lòng nhập họ tên</t>
+  </si>
+  <si>
+    <t>Số điện thoại không được trống</t>
+  </si>
+  <si>
+    <t>Địa chỉ email không hợp lệ</t>
+  </si>
+  <si>
+    <t>Số điện thoại không hợp lệ (độ dài từ 8 - 15 ký tự, không chứa ký tự đặc biệt và khoảng trắng)</t>
+  </si>
+  <si>
+    <t>Địa chỉ không được trống</t>
+  </si>
+  <si>
+    <t>Số điện thoại không hợp lệ (độ dài từ 8 - 15 ký tự, không chứa ký tự đặc biệt và khoảng trắng</t>
   </si>
 </sst>
 </file>
@@ -974,7 +971,7 @@
     <col min="5" max="5" width="11.44140625" customWidth="1"/>
     <col min="6" max="6" width="14.77734375" customWidth="1"/>
     <col min="7" max="7" width="19.88671875" customWidth="1"/>
-    <col min="8" max="8" width="24" customWidth="1"/>
+    <col min="8" max="8" width="73.33203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="31.88671875" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1050,7 +1047,7 @@
         <v>13</v>
       </c>
       <c r="H3" t="s">
-        <v>15</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.3">
@@ -1073,7 +1070,7 @@
         <v>13</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
@@ -1096,7 +1093,7 @@
         <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>25</v>
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
@@ -1104,7 +1101,7 @@
         <v>8</v>
       </c>
       <c r="B6" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="C6">
         <v>324567656</v>
@@ -1122,7 +1119,7 @@
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
@@ -1130,7 +1127,7 @@
         <v>8</v>
       </c>
       <c r="B7" t="s">
-        <v>20</v>
+        <v>16</v>
       </c>
       <c r="C7">
         <v>324567657</v>
@@ -1148,7 +1145,7 @@
         <v>13</v>
       </c>
       <c r="H7" t="s">
-        <v>19</v>
+        <v>23</v>
       </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
@@ -1174,7 +1171,7 @@
         <v>13</v>
       </c>
       <c r="H8" t="s">
-        <v>21</v>
+        <v>26</v>
       </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
@@ -1185,7 +1182,7 @@
         <v>9</v>
       </c>
       <c r="C9" t="s">
-        <v>22</v>
+        <v>17</v>
       </c>
       <c r="D9" t="s">
         <v>10</v>
@@ -1200,7 +1197,7 @@
         <v>13</v>
       </c>
       <c r="H9" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
@@ -1211,7 +1208,7 @@
         <v>9</v>
       </c>
       <c r="C10" t="s">
-        <v>23</v>
+        <v>18</v>
       </c>
       <c r="D10" t="s">
         <v>10</v>
@@ -1226,7 +1223,7 @@
         <v>13</v>
       </c>
       <c r="H10" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
@@ -1237,7 +1234,7 @@
         <v>9</v>
       </c>
       <c r="C11">
-        <v>1234567</v>
+        <v>987654321</v>
       </c>
       <c r="D11" t="s">
         <v>10</v>
@@ -1278,18 +1275,18 @@
         <v>13</v>
       </c>
       <c r="H12" t="s">
-        <v>14</v>
+        <v>24</v>
       </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
-        <v>24</v>
+        <v>19</v>
       </c>
       <c r="B13" t="s">
         <v>9</v>
       </c>
       <c r="C13">
-        <v>986547896</v>
+        <v>987654321</v>
       </c>
       <c r="D13" t="s">
         <v>10</v>
@@ -1304,7 +1301,7 @@
         <v>13</v>
       </c>
       <c r="H13" t="s">
-        <v>25</v>
+        <v>14</v>
       </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
@@ -1318,7 +1315,7 @@
         <v>986547897</v>
       </c>
       <c r="D14" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="E14" t="s">
         <v>11</v>
@@ -1330,7 +1327,7 @@
         <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>27</v>
+        <v>14</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Order_data.xlsx
+++ b/Data/Order_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{210CCBC6-BE11-4DEA-BC02-6FCCD3DD1029}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9234D53B-EFD9-46DB-BB8F-A0293C433F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4206AC39-6B44-4762-8F45-A4B4FD4DED31}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="28">
   <si>
     <t>Họ và tên</t>
   </si>
@@ -101,6 +101,9 @@
   </si>
   <si>
     <t>Số điện thoại không hợp lệ (độ dài từ 8 - 15 ký tự, không chứa ký tự đặc biệt và khoảng trắng</t>
+  </si>
+  <si>
+    <t>Địa chỉ không hợp lệ</t>
   </si>
 </sst>
 </file>
@@ -1327,7 +1330,7 @@
         <v>13</v>
       </c>
       <c r="H14" t="s">
-        <v>14</v>
+        <v>27</v>
       </c>
     </row>
   </sheetData>

--- a/Data/Order_data.xlsx
+++ b/Data/Order_data.xlsx
@@ -2,13 +2,13 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\test_TL\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9234D53B-EFD9-46DB-BB8F-A0293C433F63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC229002-4603-466E-81A8-D5DE988C4E9A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{4206AC39-6B44-4762-8F45-A4B4FD4DED31}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="28">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="99" uniqueCount="29">
   <si>
     <t>Họ và tên</t>
   </si>
@@ -104,6 +104,9 @@
   </si>
   <si>
     <t>Địa chỉ không hợp lệ</t>
+  </si>
+  <si>
+    <t>Please include an '@' in the email address.</t>
   </si>
 </sst>
 </file>
@@ -1122,7 +1125,7 @@
         <v>13</v>
       </c>
       <c r="H6" t="s">
-        <v>23</v>
+        <v>28</v>
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
